--- a/Analysis/rerun_prep/pipeline/work_after/hybrid_ablation_bootstrap_ci.xlsx
+++ b/Analysis/rerun_prep/pipeline/work_after/hybrid_ablation_bootstrap_ci.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6410256410220513</v>
+        <v>0.5897435897389743</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5623931623897436</v>
+        <v>0.5076923076876922</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7162393162353845</v>
+        <v>0.6683760683717949</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8974358974364104</v>
+        <v>0.8649572649579487</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8557264957256411</v>
+        <v>0.8211965811958846</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9343589743589743</v>
+        <v>0.9042735042748974</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7589743589743589</v>
+        <v>0.7025641025641025</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6974358974358974</v>
+        <v>0.6358974358974359</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8153846153846154</v>
+        <v>0.7641025641025641</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9076923076923077</v>
+        <v>0.8787179487179487</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8707692307692309</v>
+        <v>0.8376923076923078</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9415384615384615</v>
+        <v>0.9158974358974359</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1327393162394872</v>
+        <v>0.1363418803415385</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1162090811984487</v>
+        <v>0.1198504273517436</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1497185897440897</v>
+        <v>0.1531881410252436</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04488888888717949</v>
+        <v>0.04851773504205128</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03965213675125641</v>
+        <v>0.04322134081458974</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05066839743461538</v>
+        <v>0.05421604700947436</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6410256410220513</v>
+        <v>0.5897435897389743</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5623931623881538</v>
+        <v>0.5076923076861539</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7162393162364104</v>
+        <v>0.6683760683733334</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.919999999997436</v>
+        <v>0.8919658119625641</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8810256410225513</v>
+        <v>0.8488888888856411</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9541880341861539</v>
+        <v>0.9309401709374359</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7589743589743589</v>
+        <v>0.7025641025641025</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6974358974358974</v>
+        <v>0.6358974358974359</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9312820512820512</v>
+        <v>0.9189743589743589</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.878974358974359</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1327393162394872</v>
+        <v>0.1363418803415385</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1161320512818846</v>
+        <v>0.1199698717946154</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1497444444479487</v>
+        <v>0.1531155982886154</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.04768290598410255</v>
+        <v>0.04829024216666666</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04095461538533333</v>
+        <v>0.04185316239475641</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05453339743451281</v>
+        <v>0.05477884793360256</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6410256410220513</v>
+        <v>0.5897435897389743</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5623931623902564</v>
+        <v>0.5076923076876924</v>
       </c>
       <c r="E14" t="n">
-        <v>0.719658119649782</v>
+        <v>0.6683760683723204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9038373424974225</v>
+        <v>0.8600229095072164</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8689003436437887</v>
+        <v>0.8151202749133892</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9357388316154898</v>
+        <v>0.9007445589912499</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7589743589743589</v>
+        <v>0.7025641025641025</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6974358974358974</v>
+        <v>0.6410256410256411</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8153846153846154</v>
+        <v>0.7641025641025641</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9193298969072166</v>
+        <v>0.8859106529211342</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8855670103092784</v>
+        <v>0.8451030927835051</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9492268041237114</v>
+        <v>0.922250859106701</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1327393162394872</v>
+        <v>0.1363418803415385</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1165084401711667</v>
+        <v>0.1201745726482692</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1499786324774615</v>
+        <v>0.1534319444446667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.05243091351855669</v>
+        <v>0.0547966065314433</v>
       </c>
       <c r="D19" t="n">
-        <v>0.04633832510140463</v>
+        <v>0.04934430841858248</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05903518936564433</v>
+        <v>0.06063450386713917</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6410256410220513</v>
+        <v>0.5897435897389743</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5623931623892308</v>
+        <v>0.5076923076882051</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7196581196528206</v>
+        <v>0.6683760683712821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.8793162393158974</v>
+        <v>0.8326495726502564</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8307692307697435</v>
+        <v>0.7811880341884231</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9217094017092307</v>
+        <v>0.8813675213676923</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7589743589743589</v>
+        <v>0.7025641025641025</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6974358974358974</v>
+        <v>0.6358974358974359</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8153846153846154</v>
+        <v>0.7641025641025641</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.8964102564102565</v>
+        <v>0.8684615384615386</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8553846153846154</v>
+        <v>0.8251282051282052</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9097435897435896</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1327393162394872</v>
+        <v>0.1363418803415385</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1159785256408333</v>
+        <v>0.1196064102521667</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1499533119661282</v>
+        <v>0.1531373931635641</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.07175705128307693</v>
+        <v>0.07399957264871794</v>
       </c>
       <c r="D25" t="n">
-        <v>0.06113198718052563</v>
+        <v>0.06366577991529487</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08310725961644871</v>
+        <v>0.08513953525415384</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
